--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -8933,7 +8933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9585,6 +9585,156 @@
       <c r="J13" t="inlineStr">
         <is>
           <t>OI-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ADV-014</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>314546</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SSOT fact gate (OVERRUN) · R23 · Service Checklist</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Gearbox oil (R151F) OVERDUE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>43,346 km on the oil (changed Feb 2025 @ 271,200 km) vs 40,000 km interval — +3,346 km over. Surfaced by the odometer single-source sweep; hidden previously by a stale odometer reading.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Change gearbox oil (GL-4 75W-90 ONLY — GL-5 destroys the synchros) before departure.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>OI-108</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ADV-015</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>314546</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SSOT fact gate (OVERRUN) · R23 · Service Checklist</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Transfer case oil OVERDUE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>43,346 km on the oil (changed Feb 2025 @ 271,200 km at rebuild) vs 40,000 km interval — +3,346 km over.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Change transfer case oil before departure.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>OI-108</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ADV-016</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>314546</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SSOT fact gate (OVERRUN) · R23 · Service Checklist</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Rear differential oil OVERDUE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>41,523 km on the oil (changed Apr 2025 @ 273,023 km) vs 40,000 km interval — +1,523 km over. Front diff oil (changed Jan 2026 @ 293,949 km, 20,597 km) is within interval.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Change rear diff oil (80W-90) before departure.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>OI-108</t>
         </is>
       </c>
     </row>

--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -17,9 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;R&quot;#,##0_);[Red]\(&quot;R&quot;#,##0\)"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -629,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I310"/>
+  <dimension ref="A1:I311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.59765625" customWidth="1" min="1" max="1"/>
@@ -8912,6 +8913,37 @@
       <c r="G310" t="inlineStr">
         <is>
           <t>Enertec 650B-BLS Premium Plus Silver SMF crank battery + delivery. Invoice LC76SW004 (VAT-incl: R2,133.33 + R160.00 delivery, excl, ×1.15). Replaces Willard 650. Service item (consumable).</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B311" s="27" t="n">
+        <v>314624</v>
+      </c>
+      <c r="C311" s="1" t="inlineStr">
+        <is>
+          <t>BFG All-Terrain KO3 265/75R16 (5)</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Tyres</t>
+        </is>
+      </c>
+      <c r="E311" s="3" t="n">
+        <v>24785.95</v>
+      </c>
+      <c r="F311" s="1" t="inlineStr">
+        <is>
+          <t>First Alignment</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>BFG All-Terrain KO3 265/75R16LT load range D, LI 119/116 S — 5 tyres + balancing, invoice 20391 (VAT-incl). 4 fitted + 1 spare on existing 16" steel rims (restores the spare lost to the 3rd Maxxis sidewall puncture); replaces Maxxis AT811 (~51,624 km). Wheel alignment same day, no charge (invoice R029093).</t>
         </is>
       </c>
     </row>

--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -17,10 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;R&quot;#,##0_);[Red]\(&quot;R&quot;#,##0\)"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -9591,12 +9590,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racor fuel pre-filter — fit before expedition</t>
+          <t>Diesel fuel pre-filter — fit before expedition</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagged as a pre-expedition fitment. Relevant given the Jun 2026 fuel contamination event: tank dropped, flushed and the filter housing renewed at 310,412 km.</t>
+          <t>Flagged as a pre-expedition fitment after the Jun 2026 fuel contamination event (tank dropped/flushed, filter housing renewed @ 310,412 km). CLOSED 22 Sep 2026: fitted as a FLASHLUBE Diesel Filter (FDF), 30-micron water separator (not a Racor as originally assumed) in the Manjaro build — invoice LC76SW004, 6 Aug 2026. R4/R24 corrected to the fitted Flashlube FDF.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -9606,12 +9605,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Specify and fit during the pre-departure push. Sits with the R31 Tier 2 items in R8 timeline.</t>
+          <t>DONE — Flashlube FDF (30µ) fitted 6 Aug 2026 (Manjaro build LC76SW004).</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -9781,7 +9780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -10139,12 +10138,12 @@
     <row r="8">
       <c r="A8" s="41" t="inlineStr">
         <is>
+          <t>LED spotlights (Hella Valuefit 450 LED kit, 2× + harness)</t>
+        </is>
+      </c>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
           <t>Manjaro build — Requirements</t>
-        </is>
-      </c>
-      <c r="B8" s="41" t="inlineStr">
-        <is>
-          <t>Manjaro build</t>
         </is>
       </c>
       <c r="C8" s="41" t="inlineStr">
@@ -10179,23 +10178,23 @@
         </is>
       </c>
       <c r="J8" s="44" t="n">
-        <v>7132.13</v>
+        <v>6428.57</v>
       </c>
       <c r="K8" s="41" t="inlineStr">
         <is>
-          <t>Invoice LC76SW004. VAT-incl (excl R6,201.85 ×1.15).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Requirements). VAT-incl (excl R5,590.06 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build — Rear</t>
+          <t>Winch check &amp; service</t>
         </is>
       </c>
       <c r="B9" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build</t>
+          <t>Manjaro build — Requirements</t>
         </is>
       </c>
       <c r="C9" s="41" t="inlineStr">
@@ -10230,23 +10229,23 @@
         </is>
       </c>
       <c r="J9" s="44" t="n">
-        <v>70956</v>
+        <v>0</v>
       </c>
       <c r="K9" s="41" t="inlineStr">
         <is>
-          <t>Invoice LC76SW004. VAT-incl (excl R61,700.87 ×1.15). Includes integrated GobiX tow hitch (replaced the removed original tow bar).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Requirements). VAT-incl (excl R0.00 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build — Interior Front</t>
+          <t>Winch battery cut-off switch (M on/off w/ knob)</t>
         </is>
       </c>
       <c r="B10" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build</t>
+          <t>Manjaro build — Requirements</t>
         </is>
       </c>
       <c r="C10" s="41" t="inlineStr">
@@ -10281,23 +10280,23 @@
         </is>
       </c>
       <c r="J10" s="44" t="n">
-        <v>17517.42</v>
+        <v>703.5599999999999</v>
       </c>
       <c r="K10" s="41" t="inlineStr">
         <is>
-          <t>Invoice LC76SW004. VAT-incl (excl R15,232.54 ×1.15).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Requirements). VAT-incl (excl R611.79 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build — Interior Rear</t>
+          <t>Rear bumper — Premium Land Cruiser 76-series (Gobi-X; integrated hitch replaced the original tow bar)</t>
         </is>
       </c>
       <c r="B11" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build</t>
+          <t>Manjaro build — Rear</t>
         </is>
       </c>
       <c r="C11" s="41" t="inlineStr">
@@ -10332,23 +10331,23 @@
         </is>
       </c>
       <c r="J11" s="44" t="n">
-        <v>94718.39</v>
+        <v>19994.99</v>
       </c>
       <c r="K11" s="41" t="inlineStr">
         <is>
-          <t>Invoice LC76SW004. VAT-incl (excl R82,363.82 ×1.15). Includes integrated GobiX tow hitch (replaced the removed original tow bar).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Rear). VAT-incl (excl R17,386.96 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build — Engine Bay</t>
+          <t>Swing-arm carrier (Gadget RHS)</t>
         </is>
       </c>
       <c r="B12" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build</t>
+          <t>Manjaro build — Rear</t>
         </is>
       </c>
       <c r="C12" s="41" t="inlineStr">
@@ -10383,23 +10382,23 @@
         </is>
       </c>
       <c r="J12" s="44" t="n">
-        <v>12046.34</v>
+        <v>10000</v>
       </c>
       <c r="K12" s="41" t="inlineStr">
         <is>
-          <t>Invoice LC76SW004. VAT-incl (excl R10,475.08 ×1.15).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Rear). VAT-incl (excl R8,695.65 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build — Fire kit</t>
+          <t>Gadget PCD carrier (LC70/76/78)</t>
         </is>
       </c>
       <c r="B13" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build</t>
+          <t>Manjaro build — Rear</t>
         </is>
       </c>
       <c r="C13" s="41" t="inlineStr">
@@ -10420,7 +10419,7 @@
       </c>
       <c r="G13" s="41" t="inlineStr">
         <is>
-          <t>Removable</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="H13" s="41" t="inlineStr">
@@ -10434,23 +10433,23 @@
         </is>
       </c>
       <c r="J13" s="44" t="n">
-        <v>5574</v>
+        <v>500.01</v>
       </c>
       <c r="K13" s="41" t="inlineStr">
         <is>
-          <t>Invoice LC76SW004. VAT-incl (excl R4,846.96 ×1.15).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Rear). VAT-incl (excl R434.79 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build — Electrical (LiFePO4 system)</t>
+          <t>Hydraulic jack-plate adaptor (ARB holder)</t>
         </is>
       </c>
       <c r="B14" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build</t>
+          <t>Manjaro build — Rear</t>
         </is>
       </c>
       <c r="C14" s="41" t="inlineStr">
@@ -10485,23 +10484,23 @@
         </is>
       </c>
       <c r="J14" s="44" t="n">
-        <v>52425.53</v>
+        <v>795.01</v>
       </c>
       <c r="K14" s="41" t="inlineStr">
         <is>
-          <t>Invoice LC76SW004. VAT-incl (excl R45,587.42 ×1.15).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Rear). VAT-incl (excl R691.31 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build — Extras</t>
+          <t>Utility box (LHS carrier)</t>
         </is>
       </c>
       <c r="B15" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build</t>
+          <t>Manjaro build — Rear</t>
         </is>
       </c>
       <c r="C15" s="41" t="inlineStr">
@@ -10522,7 +10521,7 @@
       </c>
       <c r="G15" s="41" t="inlineStr">
         <is>
-          <t>Removable</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="H15" s="41" t="inlineStr">
@@ -10536,23 +10535,23 @@
         </is>
       </c>
       <c r="J15" s="44" t="n">
-        <v>15058.2</v>
+        <v>14995</v>
       </c>
       <c r="K15" s="41" t="inlineStr">
         <is>
-          <t>Invoice LC76SW004. VAT-incl (excl R13,094.09 ×1.15).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Rear). VAT-incl (excl R13,039.13 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build — Fitment labour</t>
+          <t>Stainless pop-up table (Utility '25 box)</t>
         </is>
       </c>
       <c r="B16" s="41" t="inlineStr">
         <is>
-          <t>Manjaro build</t>
+          <t>Manjaro build — Rear</t>
         </is>
       </c>
       <c r="C16" s="41" t="inlineStr">
@@ -10587,31 +10586,41 @@
         </is>
       </c>
       <c r="J16" s="44" t="n">
-        <v>52008.75</v>
+        <v>2394.99</v>
       </c>
       <c r="K16" s="41" t="inlineStr">
         <is>
-          <t>Invoice LC76SW004. VAT-incl (excl R45,225.00 ×1.15).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Rear). VAT-incl (excl R2,082.60 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="41" t="inlineStr">
         <is>
-          <t>ARB front bumper (black, winch-compatible)</t>
+          <t>Wood-top carrier (Utility '25 box)</t>
         </is>
       </c>
       <c r="B17" s="41" t="inlineStr">
         <is>
-          <t>Body &amp; armour</t>
-        </is>
-      </c>
-      <c r="C17" s="41" t="inlineStr"/>
+          <t>Manjaro build — Rear</t>
+        </is>
+      </c>
+      <c r="C17" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D17" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E17" s="43" t="inlineStr"/>
-      <c r="F17" s="41" t="inlineStr"/>
+        <v>46240</v>
+      </c>
+      <c r="E17" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F17" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G17" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -10628,31 +10637,41 @@
         </is>
       </c>
       <c r="J17" s="44" t="n">
-        <v>10395</v>
+        <v>2600</v>
       </c>
       <c r="K17" s="41" t="inlineStr">
         <is>
-          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Rear). VAT-incl (excl R2,260.87 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="41" t="inlineStr">
         <is>
-          <t>Safari snorkel</t>
+          <t>Courier — Gobi-X to Manjaro</t>
         </is>
       </c>
       <c r="B18" s="41" t="inlineStr">
         <is>
-          <t>Body &amp; armour</t>
-        </is>
-      </c>
-      <c r="C18" s="41" t="inlineStr"/>
+          <t>Manjaro build — Rear</t>
+        </is>
+      </c>
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D18" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E18" s="43" t="inlineStr"/>
-      <c r="F18" s="41" t="inlineStr"/>
+        <v>46240</v>
+      </c>
+      <c r="E18" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F18" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G18" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -10669,31 +10688,41 @@
         </is>
       </c>
       <c r="J18" s="44" t="n">
-        <v>4210</v>
+        <v>431.25</v>
       </c>
       <c r="K18" s="41" t="inlineStr">
         <is>
-          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Rear). VAT-incl (excl R375.00 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="41" t="inlineStr">
         <is>
-          <t>T-Max 9500 electric winch</t>
+          <t>Spare-wheel bin bag (Gobi-X)</t>
         </is>
       </c>
       <c r="B19" s="41" t="inlineStr">
         <is>
-          <t>Recovery &amp; armour</t>
-        </is>
-      </c>
-      <c r="C19" s="41" t="inlineStr"/>
+          <t>Manjaro build — Rear</t>
+        </is>
+      </c>
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D19" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E19" s="43" t="inlineStr"/>
-      <c r="F19" s="41" t="inlineStr"/>
+        <v>46240</v>
+      </c>
+      <c r="E19" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F19" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G19" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -10710,31 +10739,41 @@
         </is>
       </c>
       <c r="J19" s="44" t="n">
-        <v>5465</v>
+        <v>1495</v>
       </c>
       <c r="K19" s="41" t="inlineStr">
         <is>
-          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Rear). VAT-incl (excl R1,300.00 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="41" t="inlineStr">
         <is>
-          <t>Replacement 145L long-range fuel tank</t>
+          <t>20 L jerry cans / water containers (×2)</t>
         </is>
       </c>
       <c r="B20" s="41" t="inlineStr">
         <is>
-          <t>Fuel system</t>
-        </is>
-      </c>
-      <c r="C20" s="41" t="inlineStr"/>
+          <t>Manjaro build — Rear</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D20" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E20" s="43" t="inlineStr"/>
-      <c r="F20" s="41" t="inlineStr"/>
+        <v>46240</v>
+      </c>
+      <c r="E20" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F20" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G20" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -10751,31 +10790,41 @@
         </is>
       </c>
       <c r="J20" s="44" t="n">
-        <v>6760</v>
+        <v>1749.75</v>
       </c>
       <c r="K20" s="41" t="inlineStr">
         <is>
-          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Rear). VAT-incl (excl R1,521.52 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="41" t="inlineStr">
         <is>
-          <t>AOP roof rack + top rail</t>
+          <t>Front Runner aluminium gullwing window — LH</t>
         </is>
       </c>
       <c r="B21" s="41" t="inlineStr">
         <is>
-          <t>Body &amp; armour</t>
-        </is>
-      </c>
-      <c r="C21" s="41" t="inlineStr"/>
+          <t>Manjaro build — Rear</t>
+        </is>
+      </c>
+      <c r="C21" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D21" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E21" s="43" t="inlineStr"/>
-      <c r="F21" s="41" t="inlineStr"/>
+        <v>46240</v>
+      </c>
+      <c r="E21" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F21" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G21" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -10792,31 +10841,41 @@
         </is>
       </c>
       <c r="J21" s="44" t="n">
-        <v>7390</v>
+        <v>8000</v>
       </c>
       <c r="K21" s="41" t="inlineStr">
         <is>
-          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Rear). VAT-incl (excl R6,956.52 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="41" t="inlineStr">
         <is>
-          <t>AOP roof rack ladder</t>
+          <t>Front Runner aluminium gullwing window — RH</t>
         </is>
       </c>
       <c r="B22" s="41" t="inlineStr">
         <is>
-          <t>Body &amp; armour</t>
-        </is>
-      </c>
-      <c r="C22" s="41" t="inlineStr"/>
+          <t>Manjaro build — Rear</t>
+        </is>
+      </c>
+      <c r="C22" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D22" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E22" s="43" t="inlineStr"/>
-      <c r="F22" s="41" t="inlineStr"/>
+        <v>46240</v>
+      </c>
+      <c r="E22" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F22" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G22" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -10833,31 +10892,41 @@
         </is>
       </c>
       <c r="J22" s="44" t="n">
-        <v>1460</v>
+        <v>8000</v>
       </c>
       <c r="K22" s="41" t="inlineStr">
         <is>
-          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Rear). VAT-incl (excl R6,956.52 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="41" t="inlineStr">
         <is>
-          <t>Escape Canvas seat covers (full set)</t>
+          <t>T-roof console (grey, double-cab facelift)</t>
         </is>
       </c>
       <c r="B23" s="41" t="inlineStr">
         <is>
-          <t>Interior</t>
-        </is>
-      </c>
-      <c r="C23" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Front</t>
+        </is>
+      </c>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D23" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E23" s="43" t="inlineStr"/>
-      <c r="F23" s="41" t="inlineStr"/>
+        <v>46240</v>
+      </c>
+      <c r="E23" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F23" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G23" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -10874,31 +10943,41 @@
         </is>
       </c>
       <c r="J23" s="44" t="n">
-        <v>3295</v>
+        <v>13250</v>
       </c>
       <c r="K23" s="41" t="inlineStr">
         <is>
-          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Front). VAT-incl (excl R11,521.74 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="41" t="inlineStr">
         <is>
-          <t>ARB compressor (engine-bay mounted)</t>
+          <t>OneX smart rear-view mirror + dash cam (DVR, WiFi, 4K)</t>
         </is>
       </c>
       <c r="B24" s="41" t="inlineStr">
         <is>
-          <t>Recovery &amp; armour</t>
-        </is>
-      </c>
-      <c r="C24" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Front</t>
+        </is>
+      </c>
+      <c r="C24" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D24" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E24" s="43" t="inlineStr"/>
-      <c r="F24" s="41" t="inlineStr"/>
+        <v>46240</v>
+      </c>
+      <c r="E24" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F24" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G24" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -10915,31 +10994,41 @@
         </is>
       </c>
       <c r="J24" s="44" t="n">
-        <v>2850</v>
+        <v>3990.5</v>
       </c>
       <c r="K24" s="41" t="inlineStr">
         <is>
-          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Front). VAT-incl (excl R3,470.00 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="41" t="inlineStr">
         <is>
-          <t>Complete OME medium suspension (ORIGINAL build)</t>
+          <t>USB-A&amp;C charging, front dash</t>
         </is>
       </c>
       <c r="B25" s="41" t="inlineStr">
         <is>
-          <t>Suspension</t>
-        </is>
-      </c>
-      <c r="C25" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Front</t>
+        </is>
+      </c>
+      <c r="C25" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D25" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E25" s="43" t="inlineStr"/>
-      <c r="F25" s="41" t="inlineStr"/>
+        <v>46240</v>
+      </c>
+      <c r="E25" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F25" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G25" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -10956,31 +11045,41 @@
         </is>
       </c>
       <c r="J25" s="44" t="n">
-        <v>18340</v>
+        <v>276.92</v>
       </c>
       <c r="K25" s="41" t="inlineStr">
         <is>
-          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Front). VAT-incl (excl R240.80 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="41" t="inlineStr">
         <is>
-          <t>SAC low-boost turbo kit</t>
+          <t>LH door molle panel</t>
         </is>
       </c>
       <c r="B26" s="41" t="inlineStr">
         <is>
-          <t>Engine &amp; powertrain</t>
-        </is>
-      </c>
-      <c r="C26" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="C26" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D26" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E26" s="43" t="inlineStr"/>
-      <c r="F26" s="41" t="inlineStr"/>
+        <v>46240</v>
+      </c>
+      <c r="E26" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F26" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G26" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -10997,31 +11096,41 @@
         </is>
       </c>
       <c r="J26" s="44" t="n">
-        <v>17500</v>
+        <v>2546.73</v>
       </c>
       <c r="K26" s="41" t="inlineStr">
         <is>
-          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Rear). VAT-incl (excl R2,214.55 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="41" t="inlineStr">
         <is>
-          <t>EGT pyrometer gauge</t>
+          <t>LH rear-window molle plates</t>
         </is>
       </c>
       <c r="B27" s="41" t="inlineStr">
         <is>
-          <t>Engine &amp; powertrain</t>
-        </is>
-      </c>
-      <c r="C27" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="C27" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D27" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E27" s="43" t="inlineStr"/>
-      <c r="F27" s="41" t="inlineStr"/>
+        <v>46240</v>
+      </c>
+      <c r="E27" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F27" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G27" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -11038,31 +11147,41 @@
         </is>
       </c>
       <c r="J27" s="44" t="n">
-        <v>2500</v>
+        <v>3265.56</v>
       </c>
       <c r="K27" s="41" t="inlineStr">
         <is>
-          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Rear). VAT-incl (excl R2,839.62 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="41" t="inlineStr">
         <is>
-          <t>SAC intercooler + bonnet scoop</t>
+          <t>RH rear-door drop-down table + coffee station</t>
         </is>
       </c>
       <c r="B28" s="41" t="inlineStr">
         <is>
-          <t>Engine &amp; powertrain</t>
-        </is>
-      </c>
-      <c r="C28" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="C28" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D28" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E28" s="43" t="inlineStr"/>
-      <c r="F28" s="41" t="inlineStr"/>
+        <v>46240</v>
+      </c>
+      <c r="E28" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F28" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G28" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -11079,34 +11198,44 @@
         </is>
       </c>
       <c r="J28" s="44" t="n">
-        <v>13645</v>
+        <v>11076.9</v>
       </c>
       <c r="K28" s="41" t="inlineStr">
         <is>
-          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Rear). VAT-incl (excl R9,632.09 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="41" t="inlineStr">
         <is>
-          <t>National Luna 55L aluminium fridge/freezer</t>
+          <t>Drawer system (LC76_MD_Drawer_Unit)</t>
         </is>
       </c>
       <c r="B29" s="41" t="inlineStr">
         <is>
-          <t>Kitchen (portable)</t>
-        </is>
-      </c>
-      <c r="C29" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D29" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E29" s="43" t="inlineStr"/>
-      <c r="F29" s="41" t="inlineStr"/>
+        <v>46240</v>
+      </c>
+      <c r="E29" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F29" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G29" s="41" t="inlineStr">
         <is>
-          <t>Removable</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="H29" s="41" t="inlineStr">
@@ -11120,34 +11249,44 @@
         </is>
       </c>
       <c r="J29" s="44" t="n">
-        <v>7950</v>
+        <v>37118.69</v>
       </c>
       <c r="K29" s="41" t="inlineStr">
         <is>
-          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Rear). VAT-incl (excl R32,277.12 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="41" t="inlineStr">
         <is>
-          <t>OzTent RV4 + 2 side panels</t>
+          <t>Carpet for drawer system (charcoal 720 gsm, ×4)</t>
         </is>
       </c>
       <c r="B30" s="41" t="inlineStr">
         <is>
-          <t>Camping (portable)</t>
-        </is>
-      </c>
-      <c r="C30" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="C30" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D30" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E30" s="43" t="inlineStr"/>
-      <c r="F30" s="41" t="inlineStr"/>
+        <v>46240</v>
+      </c>
+      <c r="E30" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F30" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G30" s="41" t="inlineStr">
         <is>
-          <t>Removable</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="H30" s="41" t="inlineStr">
@@ -11161,34 +11300,44 @@
         </is>
       </c>
       <c r="J30" s="44" t="n">
-        <v>7995</v>
+        <v>788.5700000000001</v>
       </c>
       <c r="K30" s="41" t="inlineStr">
         <is>
-          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Rear). VAT-incl (excl R685.71 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="41" t="inlineStr">
         <is>
-          <t>MaxTrax recovery boards (×2)</t>
+          <t>Gullwing boxes (×2)</t>
         </is>
       </c>
       <c r="B31" s="41" t="inlineStr">
         <is>
-          <t>Recovery (portable)</t>
-        </is>
-      </c>
-      <c r="C31" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="C31" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D31" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E31" s="43" t="inlineStr"/>
-      <c r="F31" s="41" t="inlineStr"/>
+        <v>46240</v>
+      </c>
+      <c r="E31" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F31" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G31" s="41" t="inlineStr">
         <is>
-          <t>Removable</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="H31" s="41" t="inlineStr">
@@ -11202,29 +11351,41 @@
         </is>
       </c>
       <c r="J31" s="44" t="n">
-        <v>8600</v>
+        <v>5646.5</v>
       </c>
       <c r="K31" s="41" t="inlineStr">
         <is>
-          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Rear). VAT-incl (excl R4,910.00 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="41" t="inlineStr">
         <is>
-          <t>Indeflate 2-hose deflation/inflation unit</t>
+          <t>Shelving between gullwing boxes</t>
         </is>
       </c>
       <c r="B32" s="41" t="inlineStr">
         <is>
-          <t>Recovery &amp; armour</t>
-        </is>
-      </c>
-      <c r="C32" s="41" t="inlineStr"/>
-      <c r="D32" s="41" t="inlineStr"/>
-      <c r="E32" s="43" t="inlineStr"/>
-      <c r="F32" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="C32" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D32" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E32" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F32" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G32" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -11237,33 +11398,45 @@
       </c>
       <c r="I32" s="41" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="J32" s="44" t="n">
-        <v>4500</v>
+        <v>3744.4</v>
       </c>
       <c r="K32" s="41" t="inlineStr">
         <is>
-          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Rear). VAT-incl (excl R3,256.00 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="41" t="inlineStr">
         <is>
-          <t>ARB hydraulic jack + tyre lift</t>
+          <t>Ratchet strap for fridge</t>
         </is>
       </c>
       <c r="B33" s="41" t="inlineStr">
         <is>
-          <t>Recovery &amp; armour</t>
-        </is>
-      </c>
-      <c r="C33" s="41" t="inlineStr"/>
-      <c r="D33" s="41" t="inlineStr"/>
-      <c r="E33" s="43" t="inlineStr"/>
-      <c r="F33" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="C33" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D33" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E33" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F33" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G33" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -11276,33 +11449,45 @@
       </c>
       <c r="I33" s="41" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="J33" s="44" t="n">
-        <v>28995</v>
+        <v>138.84</v>
       </c>
       <c r="K33" s="41" t="inlineStr">
         <is>
-          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Rear). VAT-incl (excl R120.73 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="41" t="inlineStr">
         <is>
-          <t>ARB tyre repair kit</t>
+          <t>Middle floor platform</t>
         </is>
       </c>
       <c r="B34" s="41" t="inlineStr">
         <is>
-          <t>Recovery &amp; armour</t>
-        </is>
-      </c>
-      <c r="C34" s="41" t="inlineStr"/>
-      <c r="D34" s="41" t="inlineStr"/>
-      <c r="E34" s="43" t="inlineStr"/>
-      <c r="F34" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="C34" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D34" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E34" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F34" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G34" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -11315,33 +11500,45 @@
       </c>
       <c r="I34" s="41" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="J34" s="44" t="n">
-        <v>1200</v>
+        <v>2154.24</v>
       </c>
       <c r="K34" s="41" t="inlineStr">
         <is>
-          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Rear). VAT-incl (excl R1,873.25 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="41" t="inlineStr">
         <is>
-          <t>Heavy-duty jumper cables</t>
+          <t>Electric &amp; camera box</t>
         </is>
       </c>
       <c r="B35" s="41" t="inlineStr">
         <is>
-          <t>Recovery &amp; armour</t>
-        </is>
-      </c>
-      <c r="C35" s="41" t="inlineStr"/>
-      <c r="D35" s="41" t="inlineStr"/>
-      <c r="E35" s="43" t="inlineStr"/>
-      <c r="F35" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="C35" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D35" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E35" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F35" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G35" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -11354,33 +11551,45 @@
       </c>
       <c r="I35" s="41" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="J35" s="44" t="n">
-        <v>1500</v>
+        <v>15674.5</v>
       </c>
       <c r="K35" s="41" t="inlineStr">
         <is>
-          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Rear). VAT-incl (excl R13,630.00 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="41" t="inlineStr">
         <is>
-          <t>Recovery PPE (spade, gloves, glasses)</t>
+          <t>Jerry-can holder (LifeSaver 20 L + 20 L jerry)</t>
         </is>
       </c>
       <c r="B36" s="41" t="inlineStr">
         <is>
-          <t>Recovery &amp; armour</t>
-        </is>
-      </c>
-      <c r="C36" s="41" t="inlineStr"/>
-      <c r="D36" s="41" t="inlineStr"/>
-      <c r="E36" s="43" t="inlineStr"/>
-      <c r="F36" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="C36" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D36" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E36" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F36" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G36" s="41" t="inlineStr">
         <is>
           <t>Permanent</t>
@@ -11393,36 +11602,48 @@
       </c>
       <c r="I36" s="41" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="J36" s="44" t="n">
-        <v>1000</v>
+        <v>1794</v>
       </c>
       <c r="K36" s="41" t="inlineStr">
         <is>
-          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Rear). VAT-incl (excl R1,560.00 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="41" t="inlineStr">
         <is>
-          <t>Hardkorr 200W portable solar blanket</t>
+          <t>LH fridge stand + storage</t>
         </is>
       </c>
       <c r="B37" s="41" t="inlineStr">
         <is>
-          <t>Power (portable)</t>
-        </is>
-      </c>
-      <c r="C37" s="41" t="inlineStr"/>
-      <c r="D37" s="41" t="inlineStr"/>
-      <c r="E37" s="43" t="inlineStr"/>
-      <c r="F37" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="C37" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D37" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E37" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F37" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G37" s="41" t="inlineStr">
         <is>
-          <t>Removable</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="H37" s="41" t="inlineStr">
@@ -11432,36 +11653,48 @@
       </c>
       <c r="I37" s="41" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="J37" s="44" t="n">
-        <v>7725</v>
+        <v>2219.5</v>
       </c>
       <c r="K37" s="41" t="inlineStr">
         <is>
-          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Rear). VAT-incl (excl R1,930.00 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="41" t="inlineStr">
         <is>
-          <t>ARB portable jump starter</t>
+          <t>RH water stand + storage</t>
         </is>
       </c>
       <c r="B38" s="41" t="inlineStr">
         <is>
-          <t>Power (portable)</t>
-        </is>
-      </c>
-      <c r="C38" s="41" t="inlineStr"/>
-      <c r="D38" s="41" t="inlineStr"/>
-      <c r="E38" s="43" t="inlineStr"/>
-      <c r="F38" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="C38" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D38" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E38" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F38" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G38" s="41" t="inlineStr">
         <is>
-          <t>Removable</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="H38" s="41" t="inlineStr">
@@ -11471,36 +11704,48 @@
       </c>
       <c r="I38" s="41" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="J38" s="44" t="n">
-        <v>4000</v>
+        <v>2219.5</v>
       </c>
       <c r="K38" s="41" t="inlineStr">
         <is>
-          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Rear). VAT-incl (excl R1,930.00 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="41" t="inlineStr">
         <is>
-          <t>5L gas bottle + twin-top cast-iron cooker</t>
+          <t>Cam-buckle straps (LifeSaver + jerry can)</t>
         </is>
       </c>
       <c r="B39" s="41" t="inlineStr">
         <is>
-          <t>Kitchen (portable)</t>
-        </is>
-      </c>
-      <c r="C39" s="41" t="inlineStr"/>
-      <c r="D39" s="41" t="inlineStr"/>
-      <c r="E39" s="43" t="inlineStr"/>
-      <c r="F39" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="C39" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D39" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E39" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F39" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G39" s="41" t="inlineStr">
         <is>
-          <t>Removable</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="H39" s="41" t="inlineStr">
@@ -11510,36 +11755,48 @@
       </c>
       <c r="I39" s="41" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="J39" s="44" t="n">
-        <v>2000</v>
+        <v>123.91</v>
       </c>
       <c r="K39" s="41" t="inlineStr">
         <is>
-          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Rear). VAT-incl (excl R107.75 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="41" t="inlineStr">
         <is>
-          <t>Aluminium table under roof rack</t>
+          <t>RH rear-door window box</t>
         </is>
       </c>
       <c r="B40" s="41" t="inlineStr">
         <is>
-          <t>Kitchen (portable)</t>
-        </is>
-      </c>
-      <c r="C40" s="41" t="inlineStr"/>
-      <c r="D40" s="41" t="inlineStr"/>
-      <c r="E40" s="43" t="inlineStr"/>
-      <c r="F40" s="41" t="inlineStr"/>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="C40" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D40" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E40" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F40" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G40" s="41" t="inlineStr">
         <is>
-          <t>Removable</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="H40" s="41" t="inlineStr">
@@ -11549,36 +11806,48 @@
       </c>
       <c r="I40" s="41" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="J40" s="44" t="n">
-        <v>2500</v>
+        <v>6206.55</v>
       </c>
       <c r="K40" s="41" t="inlineStr">
         <is>
-          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Interior Rear). VAT-incl (excl R5,397.00 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="41" t="inlineStr">
         <is>
-          <t>Desert Fox collapsible water cells 20L (×2)</t>
+          <t>Relocate compressor; strengthen &amp; paint wheel arch</t>
         </is>
       </c>
       <c r="B41" s="41" t="inlineStr">
         <is>
-          <t>Water (portable)</t>
-        </is>
-      </c>
-      <c r="C41" s="41" t="inlineStr"/>
-      <c r="D41" s="41" t="inlineStr"/>
-      <c r="E41" s="43" t="inlineStr"/>
-      <c r="F41" s="41" t="inlineStr"/>
+          <t>Manjaro build — Engine Bay</t>
+        </is>
+      </c>
+      <c r="C41" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D41" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E41" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F41" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G41" s="41" t="inlineStr">
         <is>
-          <t>Removable</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="H41" s="41" t="inlineStr">
@@ -11588,36 +11857,48 @@
       </c>
       <c r="I41" s="41" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="J41" s="44" t="n">
-        <v>3000</v>
+        <v>172.5</v>
       </c>
       <c r="K41" s="41" t="inlineStr">
         <is>
-          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Engine Bay). VAT-incl (excl R150.00 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="41" t="inlineStr">
         <is>
-          <t>Desert Fox collapsible fuel cells 20L (×2)</t>
+          <t>Engine-bay fuse block (Safety Hub 150)</t>
         </is>
       </c>
       <c r="B42" s="41" t="inlineStr">
         <is>
-          <t>Fuel (portable)</t>
-        </is>
-      </c>
-      <c r="C42" s="41" t="inlineStr"/>
-      <c r="D42" s="41" t="inlineStr"/>
-      <c r="E42" s="43" t="inlineStr"/>
-      <c r="F42" s="41" t="inlineStr"/>
+          <t>Manjaro build — Engine Bay</t>
+        </is>
+      </c>
+      <c r="C42" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D42" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E42" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F42" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G42" s="41" t="inlineStr">
         <is>
-          <t>Removable</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="H42" s="41" t="inlineStr">
@@ -11627,36 +11908,48 @@
       </c>
       <c r="I42" s="41" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="J42" s="44" t="n">
-        <v>4000</v>
+        <v>3413.84</v>
       </c>
       <c r="K42" s="41" t="inlineStr">
         <is>
-          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Engine Bay). VAT-incl (excl R2,968.56 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="41" t="inlineStr">
         <is>
-          <t>Recovery kit (shackles, kinetic rope, snatch strap, tree protector, pulley block, dampener)</t>
+          <t>Fuse-block brackets (TR Safety Hub)</t>
         </is>
       </c>
       <c r="B43" s="41" t="inlineStr">
         <is>
-          <t>Recovery (portable)</t>
-        </is>
-      </c>
-      <c r="C43" s="41" t="inlineStr"/>
-      <c r="D43" s="41" t="inlineStr"/>
-      <c r="E43" s="43" t="inlineStr"/>
-      <c r="F43" s="41" t="inlineStr"/>
+          <t>Manjaro build — Engine Bay</t>
+        </is>
+      </c>
+      <c r="C43" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D43" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E43" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F43" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G43" s="41" t="inlineStr">
         <is>
-          <t>Removable</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="H43" s="41" t="inlineStr">
@@ -11666,36 +11959,48 @@
       </c>
       <c r="I43" s="41" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="J43" s="44" t="n">
-        <v>8000</v>
+        <v>191.54</v>
       </c>
       <c r="K43" s="41" t="inlineStr">
         <is>
-          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Engine Bay). VAT-incl (excl R166.56 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="41" t="inlineStr">
         <is>
-          <t>T-Max portable compressor</t>
+          <t>Flashlube Diesel Pre-Filter (FDF, 30µ water separator)</t>
         </is>
       </c>
       <c r="B44" s="41" t="inlineStr">
         <is>
-          <t>Recovery (portable)</t>
-        </is>
-      </c>
-      <c r="C44" s="41" t="inlineStr"/>
-      <c r="D44" s="41" t="inlineStr"/>
-      <c r="E44" s="43" t="inlineStr"/>
-      <c r="F44" s="41" t="inlineStr"/>
+          <t>Manjaro build — Engine Bay</t>
+        </is>
+      </c>
+      <c r="C44" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D44" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E44" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F44" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G44" s="41" t="inlineStr">
         <is>
-          <t>Removable</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="H44" s="41" t="inlineStr">
@@ -11705,36 +12010,48 @@
       </c>
       <c r="I44" s="41" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="J44" s="44" t="n">
-        <v>3500</v>
+        <v>3492.42</v>
       </c>
       <c r="K44" s="41" t="inlineStr">
         <is>
-          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Engine Bay). VAT-incl (excl R3,036.88 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="41" t="inlineStr">
         <is>
-          <t>SecureTech radiator seed net (800×1000mm)</t>
+          <t>FDF bracket kit</t>
         </is>
       </c>
       <c r="B45" s="41" t="inlineStr">
         <is>
-          <t>Recovery (portable)</t>
-        </is>
-      </c>
-      <c r="C45" s="41" t="inlineStr"/>
-      <c r="D45" s="41" t="inlineStr"/>
-      <c r="E45" s="43" t="inlineStr"/>
-      <c r="F45" s="41" t="inlineStr"/>
+          <t>Manjaro build — Engine Bay</t>
+        </is>
+      </c>
+      <c r="C45" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D45" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E45" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F45" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G45" s="41" t="inlineStr">
         <is>
-          <t>Removable</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="H45" s="41" t="inlineStr">
@@ -11744,36 +12061,48 @@
       </c>
       <c r="I45" s="41" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="J45" s="44" t="n">
-        <v>1500</v>
+        <v>2181.04</v>
       </c>
       <c r="K45" s="41" t="inlineStr">
         <is>
-          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Engine Bay). VAT-incl (excl R1,896.56 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="41" t="inlineStr">
         <is>
-          <t>DEFA SmartCharge portable mains battery charger</t>
+          <t>Diff breathers (ARB breather kit)</t>
         </is>
       </c>
       <c r="B46" s="41" t="inlineStr">
         <is>
-          <t>Power (portable)</t>
-        </is>
-      </c>
-      <c r="C46" s="41" t="inlineStr"/>
-      <c r="D46" s="41" t="inlineStr"/>
-      <c r="E46" s="43" t="inlineStr"/>
-      <c r="F46" s="41" t="inlineStr"/>
+          <t>Manjaro build — Engine Bay</t>
+        </is>
+      </c>
+      <c r="C46" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D46" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E46" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F46" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G46" s="41" t="inlineStr">
         <is>
-          <t>Removable</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="H46" s="41" t="inlineStr">
@@ -11783,38 +12112,48 @@
       </c>
       <c r="I46" s="41" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="J46" s="44" t="n">
-        <v>3500</v>
+        <v>2595</v>
       </c>
       <c r="K46" s="41" t="inlineStr">
         <is>
-          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Engine Bay). VAT-incl (excl R2,256.52 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="41" t="inlineStr">
         <is>
-          <t>Toyota Land Cruiser 76 Series SW — base vehicle (original purchase)</t>
+          <t>Fire Stryker aerosol suppressors (13B, ×2)</t>
         </is>
       </c>
       <c r="B47" s="41" t="inlineStr">
         <is>
-          <t>Base vehicle</t>
-        </is>
-      </c>
-      <c r="C47" s="41" t="n"/>
+          <t>Manjaro build — Fire kit</t>
+        </is>
+      </c>
+      <c r="C47" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
       <c r="D47" s="42" t="n">
-        <v>40219</v>
-      </c>
-      <c r="E47" s="43" t="n"/>
-      <c r="F47" s="41" t="n"/>
+        <v>46240</v>
+      </c>
+      <c r="E47" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F47" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
       <c r="G47" s="41" t="inlineStr">
         <is>
-          <t>Base vehicle</t>
+          <t>Removable</t>
         </is>
       </c>
       <c r="H47" s="41" t="inlineStr">
@@ -11828,28 +12167,28 @@
         </is>
       </c>
       <c r="J47" s="44" t="n">
-        <v>394000</v>
+        <v>3146.85</v>
       </c>
       <c r="K47" s="41" t="inlineStr">
         <is>
-          <t>Original vehicle purchase, 10 Feb 2010. Historical acquisition cost. Base vehicle is insured at agreed value (separate exercise), NOT this purchase cost; excluded from the accessory/build insurance schedule and from the build &amp; kit subtotal. Included in Total cost of vehicle.</t>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Fire kit). VAT-incl (excl R2,736.40 ×1.15).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="41" t="inlineStr">
         <is>
-          <t>Inmarsat IsatPhone 2.1 satellite phone + hardcase</t>
+          <t>Quickfist brackets (large, ×2)</t>
         </is>
       </c>
       <c r="B48" s="41" t="inlineStr">
         <is>
-          <t>Comms (portable)</t>
+          <t>Manjaro build — Fire kit</t>
         </is>
       </c>
       <c r="C48" s="41" t="inlineStr">
         <is>
-          <t>Global Sat4Rent</t>
+          <t>Manjaro Industries</t>
         </is>
       </c>
       <c r="D48" s="42" t="n">
@@ -11860,39 +12199,2310 @@
       </c>
       <c r="F48" s="41" t="inlineStr">
         <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G48" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H48" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I48" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J48" s="44" t="n">
+        <v>1124.99</v>
+      </c>
+      <c r="K48" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Fire kit). VAT-incl (excl R978.25 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="41" t="inlineStr">
+        <is>
+          <t>Lithium fire extinguisher (1 L)</t>
+        </is>
+      </c>
+      <c r="B49" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Fire kit</t>
+        </is>
+      </c>
+      <c r="C49" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D49" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E49" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F49" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G49" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H49" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I49" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J49" s="44" t="n">
+        <v>1302.16</v>
+      </c>
+      <c r="K49" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Fire kit). VAT-incl (excl R1,132.31 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="41" t="inlineStr">
+        <is>
+          <t>Victron MultiPlus 12/500/20-16 inverter/charger</t>
+        </is>
+      </c>
+      <c r="B50" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical</t>
+        </is>
+      </c>
+      <c r="C50" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D50" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E50" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F50" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G50" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H50" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I50" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J50" s="44" t="n">
+        <v>7061.33</v>
+      </c>
+      <c r="K50" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Electrical). VAT-incl (excl R6,140.29 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="41" t="inlineStr">
+        <is>
+          <t>Victron Orion XS 12/12-50A DC-DC charger (invoice labels 'Orion Smart'; as-built XS)</t>
+        </is>
+      </c>
+      <c r="B51" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical</t>
+        </is>
+      </c>
+      <c r="C51" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D51" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E51" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F51" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G51" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H51" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I51" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J51" s="44" t="n">
+        <v>7119.6</v>
+      </c>
+      <c r="K51" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Electrical). VAT-incl (excl R6,190.96 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="41" t="inlineStr">
+        <is>
+          <t>Victron SmartSolar MPPT 100/30</t>
+        </is>
+      </c>
+      <c r="B52" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical</t>
+        </is>
+      </c>
+      <c r="C52" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D52" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E52" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F52" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G52" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H52" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I52" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J52" s="44" t="n">
+        <v>2649.04</v>
+      </c>
+      <c r="K52" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Electrical). VAT-incl (excl R2,303.51 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="41" t="inlineStr">
+        <is>
+          <t>Victron BMV-712 Smart battery monitor</t>
+        </is>
+      </c>
+      <c r="B53" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical</t>
+        </is>
+      </c>
+      <c r="C53" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D53" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E53" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F53" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G53" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H53" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I53" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J53" s="44" t="n">
+        <v>3445.99</v>
+      </c>
+      <c r="K53" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Electrical). VAT-incl (excl R2,996.51 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="41" t="inlineStr">
+        <is>
+          <t>Victron Smart BatteryProtect 12/24V 65A</t>
+        </is>
+      </c>
+      <c r="B54" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical</t>
+        </is>
+      </c>
+      <c r="C54" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D54" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E54" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F54" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G54" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H54" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I54" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J54" s="44" t="n">
+        <v>1233.96</v>
+      </c>
+      <c r="K54" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Electrical). VAT-incl (excl R1,073.01 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="41" t="inlineStr">
+        <is>
+          <t>Dual-colour touch lights — rear doors &amp; gullwings (×4)</t>
+        </is>
+      </c>
+      <c r="B55" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical</t>
+        </is>
+      </c>
+      <c r="C55" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D55" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E55" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F55" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G55" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H55" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I55" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J55" s="44" t="n">
+        <v>1556.48</v>
+      </c>
+      <c r="K55" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Electrical). VAT-incl (excl R1,353.46 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="41" t="inlineStr">
+        <is>
+          <t>LED brackets (TR_LED_bracket v2, ×2)</t>
+        </is>
+      </c>
+      <c r="B56" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical</t>
+        </is>
+      </c>
+      <c r="C56" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D56" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E56" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F56" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G56" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H56" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I56" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J56" s="44" t="n">
+        <v>423.4</v>
+      </c>
+      <c r="K56" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Electrical). VAT-incl (excl R368.17 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="41" t="inlineStr">
+        <is>
+          <t>Fuse Block Safety Hub 150</t>
+        </is>
+      </c>
+      <c r="B57" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical</t>
+        </is>
+      </c>
+      <c r="C57" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D57" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E57" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F57" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G57" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H57" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I57" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J57" s="44" t="n">
+        <v>3413.84</v>
+      </c>
+      <c r="K57" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Electrical). VAT-incl (excl R2,968.56 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="41" t="inlineStr">
+        <is>
+          <t>Fuse block — 8-circuit mini blade</t>
+        </is>
+      </c>
+      <c r="B58" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical</t>
+        </is>
+      </c>
+      <c r="C58" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D58" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E58" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F58" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G58" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H58" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I58" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J58" s="44" t="n">
+        <v>996.46</v>
+      </c>
+      <c r="K58" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Electrical). VAT-incl (excl R866.49 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="41" t="inlineStr">
+        <is>
+          <t>Battery switch — M-series black on/off</t>
+        </is>
+      </c>
+      <c r="B59" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical</t>
+        </is>
+      </c>
+      <c r="C59" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D59" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E59" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F59" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G59" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H59" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I59" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J59" s="44" t="n">
+        <v>804.0700000000001</v>
+      </c>
+      <c r="K59" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Electrical). VAT-incl (excl R699.19 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="41" t="inlineStr">
+        <is>
+          <t>Enertec 12.8V 210 Ah LiFePO4 house battery</t>
+        </is>
+      </c>
+      <c r="B60" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical</t>
+        </is>
+      </c>
+      <c r="C60" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D60" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E60" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F60" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G60" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H60" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I60" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J60" s="44" t="n">
+        <v>16577.25</v>
+      </c>
+      <c r="K60" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Electrical). VAT-incl (excl R14,415.00 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="41" t="inlineStr">
+        <is>
+          <t>Wiring loom (LC76_MD_Electrical)</t>
+        </is>
+      </c>
+      <c r="B61" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical</t>
+        </is>
+      </c>
+      <c r="C61" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D61" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E61" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F61" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G61" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H61" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I61" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J61" s="44" t="n">
+        <v>3556.98</v>
+      </c>
+      <c r="K61" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Electrical). VAT-incl (excl R3,093.03 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="41" t="inlineStr">
+        <is>
+          <t>Shore-power extension lead (15 m, 16 A)</t>
+        </is>
+      </c>
+      <c r="B62" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical</t>
+        </is>
+      </c>
+      <c r="C62" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D62" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E62" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F62" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G62" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H62" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I62" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J62" s="44" t="n">
+        <v>623.75</v>
+      </c>
+      <c r="K62" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Electrical). VAT-incl (excl R542.39 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="41" t="inlineStr">
+        <is>
+          <t>Shore-power inlet (16 A EZ-Lock SS + enclosure)</t>
+        </is>
+      </c>
+      <c r="B63" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical</t>
+        </is>
+      </c>
+      <c r="C63" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D63" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E63" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F63" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G63" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H63" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I63" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J63" s="44" t="n">
+        <v>2495.17</v>
+      </c>
+      <c r="K63" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Electrical). VAT-incl (excl R2,169.71 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="41" t="inlineStr">
+        <is>
+          <t>Round cable bag (35 dia)</t>
+        </is>
+      </c>
+      <c r="B64" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical</t>
+        </is>
+      </c>
+      <c r="C64" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D64" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E64" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F64" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G64" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H64" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I64" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J64" s="44" t="n">
+        <v>468.21</v>
+      </c>
+      <c r="K64" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Electrical). VAT-incl (excl R407.14 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="41" t="inlineStr">
+        <is>
+          <t>LifeSaver Jerry Can water purifier 20 L (+ shower hose, membrane, carbon discs)</t>
+        </is>
+      </c>
+      <c r="B65" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Extras</t>
+        </is>
+      </c>
+      <c r="C65" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D65" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E65" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F65" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G65" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H65" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I65" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J65" s="44" t="n">
+        <v>14183.33</v>
+      </c>
+      <c r="K65" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Extras). VAT-incl (excl R12,333.33 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="41" t="inlineStr">
+        <is>
+          <t>20 L jerry can</t>
+        </is>
+      </c>
+      <c r="B66" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Extras</t>
+        </is>
+      </c>
+      <c r="C66" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D66" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E66" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F66" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G66" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H66" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I66" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J66" s="44" t="n">
+        <v>874.87</v>
+      </c>
+      <c r="K66" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Extras). VAT-incl (excl R760.76 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="41" t="inlineStr">
+        <is>
+          <t>Fitment labour (60.3 hrs @ R750)</t>
+        </is>
+      </c>
+      <c r="B67" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Labour</t>
+        </is>
+      </c>
+      <c r="C67" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D67" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E67" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F67" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G67" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H67" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I67" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J67" s="44" t="n">
+        <v>52008.75</v>
+      </c>
+      <c r="K67" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004, 6 Aug 2026 (Labour). VAT-incl (excl R45,225.00 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="41" t="inlineStr">
+        <is>
+          <t>ARB front bumper (black, winch-compatible)</t>
+        </is>
+      </c>
+      <c r="B68" s="41" t="inlineStr">
+        <is>
+          <t>Body &amp; armour</t>
+        </is>
+      </c>
+      <c r="C68" s="41" t="n"/>
+      <c r="D68" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E68" s="43" t="n"/>
+      <c r="F68" s="41" t="n"/>
+      <c r="G68" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H68" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I68" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J68" s="44" t="n">
+        <v>10395</v>
+      </c>
+      <c r="K68" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="41" t="inlineStr">
+        <is>
+          <t>Safari snorkel</t>
+        </is>
+      </c>
+      <c r="B69" s="41" t="inlineStr">
+        <is>
+          <t>Body &amp; armour</t>
+        </is>
+      </c>
+      <c r="C69" s="41" t="n"/>
+      <c r="D69" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E69" s="43" t="n"/>
+      <c r="F69" s="41" t="n"/>
+      <c r="G69" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H69" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I69" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J69" s="44" t="n">
+        <v>4210</v>
+      </c>
+      <c r="K69" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="41" t="inlineStr">
+        <is>
+          <t>T-Max 9500 electric winch</t>
+        </is>
+      </c>
+      <c r="B70" s="41" t="inlineStr">
+        <is>
+          <t>Recovery &amp; armour</t>
+        </is>
+      </c>
+      <c r="C70" s="41" t="n"/>
+      <c r="D70" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E70" s="43" t="n"/>
+      <c r="F70" s="41" t="n"/>
+      <c r="G70" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H70" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I70" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J70" s="44" t="n">
+        <v>5465</v>
+      </c>
+      <c r="K70" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="41" t="inlineStr">
+        <is>
+          <t>Replacement 145L long-range fuel tank</t>
+        </is>
+      </c>
+      <c r="B71" s="41" t="inlineStr">
+        <is>
+          <t>Fuel system</t>
+        </is>
+      </c>
+      <c r="C71" s="41" t="n"/>
+      <c r="D71" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E71" s="43" t="n"/>
+      <c r="F71" s="41" t="n"/>
+      <c r="G71" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H71" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I71" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J71" s="44" t="n">
+        <v>6760</v>
+      </c>
+      <c r="K71" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="41" t="inlineStr">
+        <is>
+          <t>AOP roof rack + top rail</t>
+        </is>
+      </c>
+      <c r="B72" s="41" t="inlineStr">
+        <is>
+          <t>Body &amp; armour</t>
+        </is>
+      </c>
+      <c r="C72" s="41" t="n"/>
+      <c r="D72" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E72" s="43" t="n"/>
+      <c r="F72" s="41" t="n"/>
+      <c r="G72" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H72" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I72" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J72" s="44" t="n">
+        <v>7390</v>
+      </c>
+      <c r="K72" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="41" t="inlineStr">
+        <is>
+          <t>AOP roof rack ladder</t>
+        </is>
+      </c>
+      <c r="B73" s="41" t="inlineStr">
+        <is>
+          <t>Body &amp; armour</t>
+        </is>
+      </c>
+      <c r="C73" s="41" t="n"/>
+      <c r="D73" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E73" s="43" t="n"/>
+      <c r="F73" s="41" t="n"/>
+      <c r="G73" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H73" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I73" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J73" s="44" t="n">
+        <v>1460</v>
+      </c>
+      <c r="K73" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="41" t="inlineStr">
+        <is>
+          <t>Escape Canvas seat covers (full set)</t>
+        </is>
+      </c>
+      <c r="B74" s="41" t="inlineStr">
+        <is>
+          <t>Interior</t>
+        </is>
+      </c>
+      <c r="C74" s="41" t="n"/>
+      <c r="D74" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E74" s="43" t="n"/>
+      <c r="F74" s="41" t="n"/>
+      <c r="G74" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H74" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I74" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J74" s="44" t="n">
+        <v>3295</v>
+      </c>
+      <c r="K74" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="41" t="inlineStr">
+        <is>
+          <t>ARB compressor (engine-bay mounted)</t>
+        </is>
+      </c>
+      <c r="B75" s="41" t="inlineStr">
+        <is>
+          <t>Recovery &amp; armour</t>
+        </is>
+      </c>
+      <c r="C75" s="41" t="n"/>
+      <c r="D75" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E75" s="43" t="n"/>
+      <c r="F75" s="41" t="n"/>
+      <c r="G75" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H75" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I75" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J75" s="44" t="n">
+        <v>2850</v>
+      </c>
+      <c r="K75" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="41" t="inlineStr">
+        <is>
+          <t>Complete OME medium suspension (ORIGINAL build)</t>
+        </is>
+      </c>
+      <c r="B76" s="41" t="inlineStr">
+        <is>
+          <t>Suspension</t>
+        </is>
+      </c>
+      <c r="C76" s="41" t="n"/>
+      <c r="D76" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E76" s="43" t="n"/>
+      <c r="F76" s="41" t="n"/>
+      <c r="G76" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H76" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I76" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J76" s="44" t="n">
+        <v>18340</v>
+      </c>
+      <c r="K76" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="41" t="inlineStr">
+        <is>
+          <t>SAC low-boost turbo kit</t>
+        </is>
+      </c>
+      <c r="B77" s="41" t="inlineStr">
+        <is>
+          <t>Engine &amp; powertrain</t>
+        </is>
+      </c>
+      <c r="C77" s="41" t="n"/>
+      <c r="D77" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E77" s="43" t="n"/>
+      <c r="F77" s="41" t="n"/>
+      <c r="G77" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H77" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I77" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J77" s="44" t="n">
+        <v>17500</v>
+      </c>
+      <c r="K77" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="41" t="inlineStr">
+        <is>
+          <t>EGT pyrometer gauge</t>
+        </is>
+      </c>
+      <c r="B78" s="41" t="inlineStr">
+        <is>
+          <t>Engine &amp; powertrain</t>
+        </is>
+      </c>
+      <c r="C78" s="41" t="n"/>
+      <c r="D78" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E78" s="43" t="n"/>
+      <c r="F78" s="41" t="n"/>
+      <c r="G78" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H78" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I78" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J78" s="44" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K78" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="41" t="inlineStr">
+        <is>
+          <t>SAC intercooler + bonnet scoop</t>
+        </is>
+      </c>
+      <c r="B79" s="41" t="inlineStr">
+        <is>
+          <t>Engine &amp; powertrain</t>
+        </is>
+      </c>
+      <c r="C79" s="41" t="n"/>
+      <c r="D79" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E79" s="43" t="n"/>
+      <c r="F79" s="41" t="n"/>
+      <c r="G79" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H79" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I79" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J79" s="44" t="n">
+        <v>13645</v>
+      </c>
+      <c r="K79" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="41" t="inlineStr">
+        <is>
+          <t>National Luna 55L aluminium fridge/freezer</t>
+        </is>
+      </c>
+      <c r="B80" s="41" t="inlineStr">
+        <is>
+          <t>Kitchen (portable)</t>
+        </is>
+      </c>
+      <c r="C80" s="41" t="n"/>
+      <c r="D80" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E80" s="43" t="n"/>
+      <c r="F80" s="41" t="n"/>
+      <c r="G80" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H80" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I80" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J80" s="44" t="n">
+        <v>7950</v>
+      </c>
+      <c r="K80" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="41" t="inlineStr">
+        <is>
+          <t>OzTent RV4 + 2 side panels</t>
+        </is>
+      </c>
+      <c r="B81" s="41" t="inlineStr">
+        <is>
+          <t>Camping (portable)</t>
+        </is>
+      </c>
+      <c r="C81" s="41" t="n"/>
+      <c r="D81" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E81" s="43" t="n"/>
+      <c r="F81" s="41" t="n"/>
+      <c r="G81" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H81" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I81" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J81" s="44" t="n">
+        <v>7995</v>
+      </c>
+      <c r="K81" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="41" t="inlineStr">
+        <is>
+          <t>MaxTrax recovery boards (×2)</t>
+        </is>
+      </c>
+      <c r="B82" s="41" t="inlineStr">
+        <is>
+          <t>Recovery (portable)</t>
+        </is>
+      </c>
+      <c r="C82" s="41" t="n"/>
+      <c r="D82" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E82" s="43" t="n"/>
+      <c r="F82" s="41" t="n"/>
+      <c r="G82" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H82" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I82" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J82" s="44" t="n">
+        <v>8600</v>
+      </c>
+      <c r="K82" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="41" t="inlineStr">
+        <is>
+          <t>Indeflate 2-hose deflation/inflation unit</t>
+        </is>
+      </c>
+      <c r="B83" s="41" t="inlineStr">
+        <is>
+          <t>Recovery &amp; armour</t>
+        </is>
+      </c>
+      <c r="C83" s="41" t="n"/>
+      <c r="D83" s="42" t="n"/>
+      <c r="E83" s="43" t="n"/>
+      <c r="F83" s="41" t="n"/>
+      <c r="G83" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H83" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I83" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J83" s="44" t="n">
+        <v>4500</v>
+      </c>
+      <c r="K83" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="41" t="inlineStr">
+        <is>
+          <t>ARB hydraulic jack + tyre lift</t>
+        </is>
+      </c>
+      <c r="B84" s="41" t="inlineStr">
+        <is>
+          <t>Recovery &amp; armour</t>
+        </is>
+      </c>
+      <c r="C84" s="41" t="n"/>
+      <c r="D84" s="42" t="n"/>
+      <c r="E84" s="43" t="n"/>
+      <c r="F84" s="41" t="n"/>
+      <c r="G84" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H84" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I84" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J84" s="44" t="n">
+        <v>28995</v>
+      </c>
+      <c r="K84" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="41" t="inlineStr">
+        <is>
+          <t>ARB tyre repair kit</t>
+        </is>
+      </c>
+      <c r="B85" s="41" t="inlineStr">
+        <is>
+          <t>Recovery &amp; armour</t>
+        </is>
+      </c>
+      <c r="C85" s="41" t="n"/>
+      <c r="D85" s="42" t="n"/>
+      <c r="E85" s="43" t="n"/>
+      <c r="F85" s="41" t="n"/>
+      <c r="G85" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H85" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I85" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J85" s="44" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K85" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="41" t="inlineStr">
+        <is>
+          <t>Heavy-duty jumper cables</t>
+        </is>
+      </c>
+      <c r="B86" s="41" t="inlineStr">
+        <is>
+          <t>Recovery &amp; armour</t>
+        </is>
+      </c>
+      <c r="C86" s="41" t="n"/>
+      <c r="D86" s="42" t="n"/>
+      <c r="E86" s="43" t="n"/>
+      <c r="F86" s="41" t="n"/>
+      <c r="G86" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H86" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I86" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J86" s="44" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K86" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="41" t="inlineStr">
+        <is>
+          <t>Recovery PPE (spade, gloves, glasses)</t>
+        </is>
+      </c>
+      <c r="B87" s="41" t="inlineStr">
+        <is>
+          <t>Recovery &amp; armour</t>
+        </is>
+      </c>
+      <c r="C87" s="41" t="n"/>
+      <c r="D87" s="42" t="n"/>
+      <c r="E87" s="43" t="n"/>
+      <c r="F87" s="41" t="n"/>
+      <c r="G87" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H87" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I87" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J87" s="44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K87" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="41" t="inlineStr">
+        <is>
+          <t>Hardkorr 200W portable solar blanket</t>
+        </is>
+      </c>
+      <c r="B88" s="41" t="inlineStr">
+        <is>
+          <t>Power (portable)</t>
+        </is>
+      </c>
+      <c r="C88" s="41" t="n"/>
+      <c r="D88" s="42" t="n"/>
+      <c r="E88" s="43" t="n"/>
+      <c r="F88" s="41" t="n"/>
+      <c r="G88" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H88" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I88" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J88" s="44" t="n">
+        <v>7725</v>
+      </c>
+      <c r="K88" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="41" t="inlineStr">
+        <is>
+          <t>ARB portable jump starter</t>
+        </is>
+      </c>
+      <c r="B89" s="41" t="inlineStr">
+        <is>
+          <t>Power (portable)</t>
+        </is>
+      </c>
+      <c r="C89" s="41" t="n"/>
+      <c r="D89" s="42" t="n"/>
+      <c r="E89" s="43" t="n"/>
+      <c r="F89" s="41" t="n"/>
+      <c r="G89" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H89" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I89" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J89" s="44" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K89" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="41" t="inlineStr">
+        <is>
+          <t>5L gas bottle + twin-top cast-iron cooker</t>
+        </is>
+      </c>
+      <c r="B90" s="41" t="inlineStr">
+        <is>
+          <t>Kitchen (portable)</t>
+        </is>
+      </c>
+      <c r="C90" s="41" t="n"/>
+      <c r="D90" s="42" t="n"/>
+      <c r="E90" s="43" t="n"/>
+      <c r="F90" s="41" t="n"/>
+      <c r="G90" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H90" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I90" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J90" s="44" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K90" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="41" t="inlineStr">
+        <is>
+          <t>Aluminium table under roof rack</t>
+        </is>
+      </c>
+      <c r="B91" s="41" t="inlineStr">
+        <is>
+          <t>Kitchen (portable)</t>
+        </is>
+      </c>
+      <c r="C91" s="41" t="n"/>
+      <c r="D91" s="42" t="n"/>
+      <c r="E91" s="43" t="n"/>
+      <c r="F91" s="41" t="n"/>
+      <c r="G91" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H91" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I91" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J91" s="44" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K91" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="41" t="inlineStr">
+        <is>
+          <t>Desert Fox collapsible water cells 20L (×2)</t>
+        </is>
+      </c>
+      <c r="B92" s="41" t="inlineStr">
+        <is>
+          <t>Water (portable)</t>
+        </is>
+      </c>
+      <c r="C92" s="41" t="n"/>
+      <c r="D92" s="42" t="n"/>
+      <c r="E92" s="43" t="n"/>
+      <c r="F92" s="41" t="n"/>
+      <c r="G92" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H92" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I92" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J92" s="44" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K92" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="41" t="inlineStr">
+        <is>
+          <t>Desert Fox collapsible fuel cells 20L (×2)</t>
+        </is>
+      </c>
+      <c r="B93" s="41" t="inlineStr">
+        <is>
+          <t>Fuel (portable)</t>
+        </is>
+      </c>
+      <c r="C93" s="41" t="n"/>
+      <c r="D93" s="42" t="n"/>
+      <c r="E93" s="43" t="n"/>
+      <c r="F93" s="41" t="n"/>
+      <c r="G93" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H93" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I93" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J93" s="44" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K93" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="41" t="inlineStr">
+        <is>
+          <t>Recovery kit (shackles, kinetic rope, snatch strap, tree protector, pulley block, dampener)</t>
+        </is>
+      </c>
+      <c r="B94" s="41" t="inlineStr">
+        <is>
+          <t>Recovery (portable)</t>
+        </is>
+      </c>
+      <c r="C94" s="41" t="n"/>
+      <c r="D94" s="42" t="n"/>
+      <c r="E94" s="43" t="n"/>
+      <c r="F94" s="41" t="n"/>
+      <c r="G94" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H94" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I94" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J94" s="44" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K94" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="41" t="inlineStr">
+        <is>
+          <t>T-Max portable compressor</t>
+        </is>
+      </c>
+      <c r="B95" s="41" t="inlineStr">
+        <is>
+          <t>Recovery (portable)</t>
+        </is>
+      </c>
+      <c r="C95" s="41" t="n"/>
+      <c r="D95" s="42" t="n"/>
+      <c r="E95" s="43" t="n"/>
+      <c r="F95" s="41" t="n"/>
+      <c r="G95" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H95" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I95" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J95" s="44" t="n">
+        <v>3500</v>
+      </c>
+      <c r="K95" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="41" t="inlineStr">
+        <is>
+          <t>SecureTech radiator seed net (800×1000mm)</t>
+        </is>
+      </c>
+      <c r="B96" s="41" t="inlineStr">
+        <is>
+          <t>Recovery (portable)</t>
+        </is>
+      </c>
+      <c r="C96" s="41" t="n"/>
+      <c r="D96" s="42" t="n"/>
+      <c r="E96" s="43" t="n"/>
+      <c r="F96" s="41" t="n"/>
+      <c r="G96" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H96" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I96" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J96" s="44" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K96" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="41" t="inlineStr">
+        <is>
+          <t>DEFA SmartCharge portable mains battery charger</t>
+        </is>
+      </c>
+      <c r="B97" s="41" t="inlineStr">
+        <is>
+          <t>Power (portable)</t>
+        </is>
+      </c>
+      <c r="C97" s="41" t="n"/>
+      <c r="D97" s="42" t="n"/>
+      <c r="E97" s="43" t="n"/>
+      <c r="F97" s="41" t="n"/>
+      <c r="G97" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H97" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I97" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J97" s="44" t="n">
+        <v>3500</v>
+      </c>
+      <c r="K97" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="41" t="inlineStr">
+        <is>
+          <t>Toyota Land Cruiser 76 Series SW — base vehicle (original purchase)</t>
+        </is>
+      </c>
+      <c r="B98" s="41" t="inlineStr">
+        <is>
+          <t>Base vehicle</t>
+        </is>
+      </c>
+      <c r="C98" s="41" t="n"/>
+      <c r="D98" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E98" s="43" t="n"/>
+      <c r="F98" s="41" t="n"/>
+      <c r="G98" s="41" t="inlineStr">
+        <is>
+          <t>Base vehicle</t>
+        </is>
+      </c>
+      <c r="H98" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I98" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J98" s="44" t="n">
+        <v>394000</v>
+      </c>
+      <c r="K98" s="41" t="inlineStr">
+        <is>
+          <t>Original vehicle purchase, 10 Feb 2010. Historical acquisition cost. Base vehicle is insured at agreed value (separate exercise), NOT this purchase cost; excluded from the accessory/build insurance schedule and from the build &amp; kit subtotal. Included in Total cost of vehicle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="41" t="inlineStr">
+        <is>
+          <t>Inmarsat IsatPhone 2.1 satellite phone + hardcase</t>
+        </is>
+      </c>
+      <c r="B99" s="41" t="inlineStr">
+        <is>
+          <t>Comms (portable)</t>
+        </is>
+      </c>
+      <c r="C99" s="41" t="inlineStr">
+        <is>
+          <t>Global Sat4Rent</t>
+        </is>
+      </c>
+      <c r="D99" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E99" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F99" s="41" t="inlineStr">
+        <is>
           <t>Invoice 8984</t>
         </is>
       </c>
-      <c r="G48" s="41" t="inlineStr">
+      <c r="G99" s="41" t="inlineStr">
         <is>
           <t>Removable</t>
         </is>
       </c>
-      <c r="H48" s="41" t="inlineStr">
+      <c r="H99" s="41" t="inlineStr">
         <is>
           <t>Fitted</t>
         </is>
       </c>
-      <c r="I48" s="41" t="inlineStr">
+      <c r="I99" s="41" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="J48" s="44" t="n">
+      <c r="J99" s="44" t="n">
         <v>21924.25</v>
       </c>
-      <c r="K48" s="41" t="inlineStr">
+      <c r="K99" s="41" t="inlineStr">
         <is>
           <t>IsatPhone Pro Prepay Regional Plan 2018, 20 units, expires 7 Aug 2027. MSISDN +870 777 751 134. ICC ID 898709925417152692. Not insured under motor policy — recorded for completeness.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="45" t="inlineStr">
-        <is>
-          <t>CONVENTION: Master of fitted kit &amp; acquisition cost — separate from Services (maintenance/repair). Insurance valuation is the derived VALUE view (filters this sheet by Fitment type / Status). Basis: Cost = actual invoice amount (VAT-incl). Replacement = current replacement value where no cost is on record (flagged). Status Removed-superseded excluded from insurance value. Original tow bar removed; replacement GobiX hitch is part of the Manjaro rear-bumper build (Rear row). DEFA SmartCharge retained as a portable spare (backup to shore-power-via-MultiPlus). Reclassification 2026-08-06. ROW ADDED 2026-08-06: base vehicle (original purchase 10 Feb 2010, R394,000) as Fitment type "Base vehicle" — build &amp; kit subtotal (45 rows) R544,082.76; TOTAL COST OF VEHICLE (46 rows, base + build &amp; kit) R938,082.76. Base vehicle excluded from the insurance accessory schedule (insured at agreed value, not purchase cost). ROW ADDED 2026-08-07: Inmarsat IsatPhone 2.1 (Global Sat4Rent, invoice 8984, R21,924.25 incl. VAT, 6 Aug 2026 @ 311,263 km) as Removable/Fitted/Cost. Satellite voice phone for emergency calls — not insured under motor policy, recorded as asset. 47 rows now.</t>
-        </is>
-      </c>
+    <row r="100">
+      <c r="A100" s="41" t="inlineStr">
+        <is>
+          <t>CONVENTION: Master of fitted kit &amp; acquisition cost — separate from Services (maintenance/repair). Insurance valuation is the derived VALUE view (filters this sheet by Fitment type / Status). Basis: Cost = actual invoice amount (VAT-incl). Replacement = current replacement value where no cost is on record (flagged). Status Removed-superseded excluded from insurance value. Original tow bar removed; replacement GobiX hitch is part of the Manjaro rear-bumper build (Rear row). DEFA SmartCharge retained as a portable spare (backup to shore-power-via-MultiPlus). Reclassification 2026-08-06. ROW ADDED 2026-08-06: base vehicle (original purchase 10 Feb 2010, R394,000) as Fitment type "Base vehicle" — build &amp; kit subtotal (45 rows) R544,082.76; TOTAL COST OF VEHICLE (46 rows, base + build &amp; kit) R938,082.76. Base vehicle excluded from the insurance accessory schedule (insured at agreed value, not purchase cost). ROW ADDED 2026-08-07: Inmarsat IsatPhone 2.1 (Global Sat4Rent, invoice 8984, R21,924.25 incl. VAT, 6 Aug 2026 @ 311,263 km) as Removable/Fitted/Cost. Satellite voice phone for emergency calls — not insured under motor policy, recorded as asset. 47 rows now. ROW-LEVEL ITEMISATION 2026-09-22: the 8 generic Manjaro build buckets were replaced with the ~60 line items from invoice LC76SW004 (6 Aug 2026), each VAT-incl (excl ×1.15), reconciled section-by-section to the former bucket totals to the cent (Manjaro build unchanged at R327,436.76; crank battery + delivery excluded — held in Services). Current totals (satphone-inclusive): build &amp; kit R566,007.01; TOTAL COST OF VEHICLE R960,007.01 (base R394,000 + build &amp; kit R566,007.01); fitted kit value R563,586.01 (R456,759.56 permanent + R106,826.45 removable). The earlier R938,082.76 / R544,082.76 figures predated the 7 Aug satphone row and are superseded. Build Register and the R8 TCO roll-up regenerated to match, 22 Sep 2026. ITEMISED 2026-09-22: the 8 generic Manjaro-build bucket rows were replaced with the ~60 individual line items from invoice LC76SW004 (6 Aug 2026), each VAT-incl (excl ×1.15); each invoice section still foots to its former bucket, so the Manjaro total (R327,436.76), the Permanent/Removable split and all downstream totals are unchanged. CURRENT TOTALS (satphone-inclusive): build &amp; kit subtotal R566,007.01; TOTAL COST OF VEHICLE R960,007.01 (base R394,000 + build &amp; kit); fitted kit value R563,586.01 (Permanent R456,759.56 + Removable R106,826.45). NOTE: the earlier R938,082.76 / R544,082.76 figures predated the 6 Aug 2026 satphone row; corrected here and in the Build Register on 2026-09-22.</t>
+        </is>
+      </c>
+      <c r="B100" s="41" t="n"/>
+      <c r="C100" s="41" t="n"/>
+      <c r="D100" s="42" t="n"/>
+      <c r="E100" s="43" t="n"/>
+      <c r="F100" s="41" t="n"/>
+      <c r="G100" s="41" t="n"/>
+      <c r="H100" s="41" t="n"/>
+      <c r="I100" s="41" t="n"/>
+      <c r="J100" s="44" t="n"/>
+      <c r="K100" s="41" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -9364,12 +9364,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Visual check at next service. Fit before any expedition water crossings if absent.</t>
+          <t>DONE — ARB breather kit fitted to the front and rear diffs 6 Aug 2026 (Manjaro build, invoice LC76SW004; Build_Accessories row 46). Gearbox and transfer-case vents are standard. Closed 4 Oct 2026 on the ledger row and the owner statement. Was: Visual check at next service. Fit before any expedition water crossings if absent.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">

--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I311"/>
+  <dimension ref="A1:I339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.59765625" customWidth="1" min="1" max="1"/>
@@ -8943,6 +8943,809 @@
       <c r="G311" t="inlineStr">
         <is>
           <t>BFG All-Terrain KO3 265/75R16LT load range D, LI 119/116 S — 5 tyres + balancing, invoice 20391 (VAT-incl). 4 fitted + 1 spare on existing 16" steel rims (restores the spare lost to the 3rd Maxxis sidewall puncture); replaces Maxxis AT811 (~51,624 km). Wheel alignment same day, no charge (invoice R029093).</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B312" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C312" s="1" t="inlineStr">
+        <is>
+          <t>Service 315,000 km - labour</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Workshop labour (service &amp; repairs)</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="n">
+        <v>34500</v>
+      </c>
+      <c r="F312" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>PW Auto Centre invoice 299944, 8 Oct 2026. Visit total R74,548.24 incl VAT = material R34,074.56 + labour R30,000.00 + sundries R750.00 (excl) + VAT R9,723.68. Each line entered x1.15. Labour covers the whole visit (service, bearings, knuckles, gaskets). The R30,000 'deposit paid' written on the invoice is a payment towards this work, not a separate charge (owner, 20 Oct 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B313" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C313" s="1" t="inlineStr">
+        <is>
+          <t>Sundries</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Workshop labour (service &amp; repairs)</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="n">
+        <v>862.5</v>
+      </c>
+      <c r="F313" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B314" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C314" s="1" t="inlineStr">
+        <is>
+          <t>Engin oil</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Manufacturers service 315,000 km</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="n">
+        <v>1495.99</v>
+      </c>
+      <c r="F314" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B315" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C315" s="1" t="inlineStr">
+        <is>
+          <t>O-rings (x8)</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Manufacturers service 315,000 km</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="n">
+        <v>271.4</v>
+      </c>
+      <c r="F315" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B316" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C316" s="1" t="inlineStr">
+        <is>
+          <t>Filter kit (oil, fuel, air)</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Manufacturers service 315,000 km</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="n">
+        <v>2816.42</v>
+      </c>
+      <c r="F316" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Terrain Tamer full filter kit (owner, 20 Oct 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B317" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C317" s="1" t="inlineStr">
+        <is>
+          <t>Brake cleaner</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Manufacturers service 315,000 km</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="F317" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B318" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C318" s="1" t="inlineStr">
+        <is>
+          <t>Grease propshaft + suspension (x2)</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Manufacturers service 315,000 km</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="F318" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B319" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C319" s="1" t="inlineStr">
+        <is>
+          <t>Coolant top up</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Cooling system</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="F319" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Top-up only - not a flush (OI-62 stays open).</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B320" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C320" s="1" t="inlineStr">
+        <is>
+          <t>Brake &amp; clutch fluid - bleed and change</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Manufacturers service 315,000 km</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="F320" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Full bleed and change, brakes and clutch (owner, 20 Oct 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B321" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C321" s="1" t="inlineStr">
+        <is>
+          <t>Powersteering fluid top up</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Manufacturers service 315,000 km</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="F321" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B322" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C322" s="1" t="inlineStr">
+        <is>
+          <t>Gearbox oil</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Manufacturers service 315,000 km</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="n">
+        <v>4347</v>
+      </c>
+      <c r="F322" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Invoice line 'Replace all gear oils' R3,780.00 excl covers gearbox, transfer case, front diff and rear diff (all four, owner 20 Oct 2026); the three rows below are its cost-0 children.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B323" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C323" s="1" t="inlineStr">
+        <is>
+          <t>Transfer case oil</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Manufacturers service 315,000 km</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F323" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B324" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C324" s="1" t="inlineStr">
+        <is>
+          <t>Diff oil - front</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Manufacturers service 315,000 km</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F324" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B325" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C325" s="1" t="inlineStr">
+        <is>
+          <t>Diff oil - rear</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Manufacturers service 315,000 km</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F325" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B326" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C326" s="1" t="inlineStr">
+        <is>
+          <t>Wheel bearing kits rear (heavy duty) (x2)</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Axles &amp; hubs</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="n">
+        <v>5725.49</v>
+      </c>
+      <c r="F326" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Kits include new rear hub seals (owner, 20 Oct 2026) - fixes the rear hub seal weep flagged Apr 2026. No oil on the handbrake shoes was reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B327" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C327" s="1" t="inlineStr">
+        <is>
+          <t>Wheel bearing grease (front + rear)</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Axles &amp; hubs</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="F327" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Front bearings repacked; rear bearings new.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B328" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C328" s="1" t="inlineStr">
+        <is>
+          <t>Lock bolts - rear adjusting nuts (x4)</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Axles &amp; hubs</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="n">
+        <v>455.86</v>
+      </c>
+      <c r="F328" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B329" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C329" s="1" t="inlineStr">
+        <is>
+          <t>Front wheel adjusting nuts (x2)</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Axles &amp; hubs</t>
+        </is>
+      </c>
+      <c r="E329" s="3" t="n">
+        <v>678.04</v>
+      </c>
+      <c r="F329" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B330" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C330" s="1" t="inlineStr">
+        <is>
+          <t>Machine rear axle shaft flanges (x2)</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Axles &amp; hubs</t>
+        </is>
+      </c>
+      <c r="E330" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="F330" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Rear axle flanges (owner, 20 Oct 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B331" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C331" s="1" t="inlineStr">
+        <is>
+          <t>Repair thread - right rear stub axle</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Axles &amp; hubs</t>
+        </is>
+      </c>
+      <c r="E331" s="3" t="n">
+        <v>517.5</v>
+      </c>
+      <c r="F331" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Rear stub axle (owner, 20 Oct 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B332" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C332" s="1" t="inlineStr">
+        <is>
+          <t>Steering knuckle kit (both sides)</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Axles &amp; hubs</t>
+        </is>
+      </c>
+      <c r="E332" s="3" t="n">
+        <v>15749.94</v>
+      </c>
+      <c r="F332" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Both sides (owner, 20 Oct 2026) - fixes the front knuckle grease leak flagged Apr 2026. Handwriting reads as R13,695.60; this is the reading that makes the lines foot to the invoice material total of R34,074.56.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B333" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C333" s="1" t="inlineStr">
+        <is>
+          <t>CV grease</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Axles &amp; hubs</t>
+        </is>
+      </c>
+      <c r="E333" s="3" t="n">
+        <v>552</v>
+      </c>
+      <c r="F333" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Birfields re-greased with the knuckle kit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B334" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C334" s="1" t="inlineStr">
+        <is>
+          <t>Valve cover gasket</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Engine gaskets</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="n">
+        <v>1015.16</v>
+      </c>
+      <c r="F334" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Rocker cover gasket and half-moon seal replaced; the crankcase breather routing was checked by the workshop first (owner, 20 Oct 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B335" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C335" s="1" t="inlineStr">
+        <is>
+          <t>Intake manifold gasket set</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Engine gaskets</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="n">
+        <v>1934.73</v>
+      </c>
+      <c r="F335" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Some sweating found at the intake manifold (owner, 20 Oct 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B336" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C336" s="1" t="inlineStr">
+        <is>
+          <t>Intake washers (x12)</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Engine gaskets</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="n">
+        <v>561.46</v>
+      </c>
+      <c r="F336" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B337" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C337" s="1" t="inlineStr">
+        <is>
+          <t>Turbo sweating at large pipe</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F337" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Mechanic advises having the turbo checked: it seems to be sweating a bit at the large pipe on the left side as you look at the car (owner, 20 Oct 2026). Advisories ADV-017.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B338" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C338" s="1" t="inlineStr">
+        <is>
+          <t>Shocks Front (OME - Nitrocharger Plus 63008) (x2)</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Suspension</t>
+        </is>
+      </c>
+      <c r="E338" s="3" t="n">
+        <v>6595.41</v>
+      </c>
+      <c r="F338" s="1" t="inlineStr">
+        <is>
+          <t>4X4 Megaworld</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>4x4 Megaworld invoice 03INV19018, 20 Oct 2026 (VAT-incl; visit total R7,295.42). Replaces the OME N181 front shocks (G-Tec, Apr 2023 @ 221,000 km), found leaking by PW Auto Centre at the 8 Oct 2026 service. Odometer not on the invoice - the 8 Oct reading (314,819 km) is used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B339" s="27" t="n">
+        <v>314819</v>
+      </c>
+      <c r="C339" s="1" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Suspension</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="n">
+        <v>700.01</v>
+      </c>
+      <c r="F339" s="1" t="inlineStr">
+        <is>
+          <t>4X4 Megaworld</t>
         </is>
       </c>
     </row>
@@ -8964,7 +9767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9034,7 +9837,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADV-001</t>
+          <t>ADV-003</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9052,22 +9855,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rear hub seal weeping</t>
+          <t>Water pump — no replacement record</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hub seal weeping; risk of gear oil tracking onto rear brake shoes. Rear drums are the primary parking brake — oil-contaminated shoes lose friction entirely. Shoes replaced Jan 2026 @ 293,949 km.</t>
+          <t>No replacement on record in 316 service entries. Weep hole dry at 308,248 km and again at 308,500 km.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Confirm which side. Check both rear drums for contamination. Wet shoe = immediate seal + shoe replacement, do not drive.</t>
+          <t>Replace proactively; bundle with timing belt (RA-3) and thermostat at the same rocker-cover-off visit.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -9077,23 +9880,23 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>OI-61</t>
+          <t>OI-62</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADV-002</t>
+          <t>ADV-004</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>308248</v>
+        <v>264347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -9102,22 +9905,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Front knuckle grease leak</t>
+          <t>Radiator quality flagged at install</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Birfield CV joints run inside the knuckle housing packed with grease. Loss of grease means the birfield runs dry; wear then accelerates to CV failure. Knuckle kit replaced Feb 2025 @ 271,200 km.</t>
+          <t>Replaced Nov 2024 @ 264,347 km by G-Tec (R10,149). Quality flagged as poor by PW at the time.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Confirm side. Re-pack with molybdenum disulphide birfield grease, inspect seal face, replace seal if damaged. Do not leave for the field.</t>
+          <t>Monitor. Budget for heavy-duty replacement before the expedition. Feeds RA-5.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -9127,14 +9930,14 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>OI-61</t>
+          <t>OI-6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADV-003</t>
+          <t>ADV-006</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9147,27 +9950,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PW Auto Centre</t>
+          <t>R8 analysis</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Water pump — no replacement record</t>
+          <t>Thermostat — no record</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No replacement on record in 316 service entries. Weep hole dry at 308,248 km and again at 308,500 km.</t>
+          <t>No thermostat replacement on record. Stuck-closed thermostat is a top-three 1HZ overheating cause. 82degC OEM spec — do not fit lower-temperature variants.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Replace proactively; bundle with timing belt (RA-3) and thermostat at the same rocker-cover-off visit.</t>
+          <t>Replace at next workshop visit. Combine with coolant flush and pressure test. Carry removed unit as field spare.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -9184,30 +9987,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADV-004</t>
+          <t>ADV-008</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-11</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>264347</v>
+          <t>2026-04-14</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PW Auto Centre</t>
+          <t>R8 analysis</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Radiator quality flagged at install</t>
+          <t>Diff breather extensions — status unknown</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Replaced Nov 2024 @ 264,347 km by G-Tec (R10,149). Quality flagged as poor by PW at the time.</t>
+          <t>Standard Toyota breathers are inadequate for water crossings above ankle depth. Extended breathers route front diff, rear diff and transfer vents high in the engine bay. Cross-ref R31 S3 item 7.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -9217,24 +10017,24 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Monitor. Budget for heavy-duty replacement before the expedition. Feeds RA-5.</t>
+          <t>DONE — ARB breather kit fitted to the front and rear diffs 6 Aug 2026 (Manjaro build, invoice LC76SW004; Build_Accessories row 46). Gearbox and transfer-case vents are standard. Closed 4 Oct 2026 on the ledger row and the owner statement. Was: Visual check at next service. Fit before any expedition water crossings if absent.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>OI-6</t>
+          <t>OI-64</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADV-006</t>
+          <t>ADV-009</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9252,22 +10052,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Thermostat — no record</t>
+          <t>Coolant flush overdue</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No thermostat replacement on record. Stuck-closed thermostat is a top-three 1HZ overheating cause. 82degC OEM spec — do not fit lower-temperature variants.</t>
+          <t>Only one flush on record — Aug 2023 @ 224,406 km. Approximately 86,006 km overdue.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Replace at next workshop visit. Combine with coolant flush and pressure test. Carry removed unit as field spare.</t>
+          <t>Schedule before the expedition; bundle with thermostat and pressure test.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -9284,7 +10084,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADV-007</t>
+          <t>ADV-010</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -9297,27 +10097,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>R8 analysis</t>
+          <t>PW Auto Centre</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wheel bearing repack overdue</t>
+          <t>Boost pipe clamp condition unconfirmed</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bearings replaced Feb 2025 @ 271,200 km but last repack ~245,000 km. Severe-use interval is 20,000 km — approximately 63,684 km overdue.</t>
+          <t>Visual check only at Apr 2026 service; clamp condition not confirmed. A boost leak drops power and raises EGT.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Front + rear repack with Toyota-spec grease. Inspect seals. Combine with brake inspection and ADV-001.</t>
+          <t>Inspect at next service (~315,000 km).</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -9327,34 +10127,34 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>OI-63</t>
+          <t>OI-75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADV-008</t>
+          <t>ADV-013</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>R8 analysis</t>
+          <t>R8 supplement (Service Checklist)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Diff breather extensions — status unknown</t>
+          <t>Diesel fuel pre-filter — fit before expedition</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Standard Toyota breathers are inadequate for water crossings above ankle depth. Extended breathers route front diff, rear diff and transfer vents high in the engine bay. Cross-ref R31 S3 item 7.</t>
+          <t>Flagged as a pre-expedition fitment after the Jun 2026 fuel contamination event (tank dropped/flushed, filter housing renewed @ 310,412 km). CLOSED 22 Sep 2026: fitted as a FLASHLUBE Diesel Filter (FDF), 30-micron water separator (not a Racor as originally assumed) in the Manjaro build — invoice LC76SW004, 6 Aug 2026. R4/R24 corrected to the fitted Flashlube FDF.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -9364,7 +10164,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DONE — ARB breather kit fitted to the front and rear diffs 6 Aug 2026 (Manjaro build, invoice LC76SW004; Build_Accessories row 46). Gearbox and transfer-case vents are standard. Closed 4 Oct 2026 on the ledger row and the owner statement. Was: Visual check at next service. Fit before any expedition water crossings if absent.</t>
+          <t>DONE — Flashlube FDF (30µ) fitted 6 Aug 2026 (Manjaro build LC76SW004).</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -9374,37 +10174,37 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>OI-64</t>
+          <t>OI-11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADV-009</t>
+          <t>ADV-017</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>308248</v>
+        <v>314819</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>R8 analysis</t>
+          <t>PW Auto Centre</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Coolant flush overdue</t>
+          <t>Turbo — oil sweat at the large pipe</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Only one flush on record — Aug 2023 @ 224,406 km. Approximately 86,006 km overdue.</t>
+          <t>Mechanic advises having the turbo checked: it seems to be sweating a bit at the large pipe on the left side as you look at the car (owner report, 20 Oct 2026). Turbo recon Aug 2023 @ 224,406 km.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -9414,7 +10214,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schedule before the expedition; bundle with thermostat and pressure test.</t>
+          <t>Have a diesel/turbo workshop inspect: identify the pipe and where the oil comes from (turbo seal, oil feed or drain, or a pipe joint). Check the boost-pipe clamps (ADV-010) at the same visit.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -9424,348 +10224,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>OI-62</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ADV-010</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>308248</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PW Auto Centre</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Boost pipe clamp condition unconfirmed</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Visual check only at Apr 2026 service; clamp condition not confirmed. A boost leak drops power and raises EGT.</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Inspect at next service (~315,000 km).</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>OI-75</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ADV-011</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>R8 supplement (Service Checklist)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Rocker cover gasket + half-moon seal — replace</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Flagged CRITICAL. First and most cost-effective intervention for the cylinder head oil seepage monitor. Genuine Toyota rocker cover gasket + front/rear grommets + reseal half-moon plug (11183-54011).</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Combine with tappet inspection — the rocker cover is already off at that event, and again at the RA-3 timing belt.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>OI-66</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ADV-012</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>R8 supplement (Service Checklist)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>PCV / crankcase breather routing — verify</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Flagged CRITICAL. If the breather is routed post-intercooler rather than pre-turbo, boost can back-pressurise the crankcase and force oil out at every top-end seal — which would directly explain the head seepage. Never verified.</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Trace the breather hose from valve cover to intake at the next visit to a 1HZ-experienced workshop. Diagnose BEFORE replacing the rocker gasket, or the gasket may simply fail again.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>OI-66</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ADV-013</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>R8 supplement (Service Checklist)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Diesel fuel pre-filter — fit before expedition</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Flagged as a pre-expedition fitment after the Jun 2026 fuel contamination event (tank dropped/flushed, filter housing renewed @ 310,412 km). CLOSED 22 Sep 2026: fitted as a FLASHLUBE Diesel Filter (FDF), 30-micron water separator (not a Racor as originally assumed) in the Manjaro build — invoice LC76SW004, 6 Aug 2026. R4/R24 corrected to the fitted Flashlube FDF.</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>DONE — Flashlube FDF (30µ) fitted 6 Aug 2026 (Manjaro build LC76SW004).</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>OI-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ADV-014</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>314546</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SSOT fact gate (OVERRUN) · R23 · Service Checklist</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Gearbox oil (R151F) OVERDUE</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>43,346 km on the oil (changed Feb 2025 @ 271,200 km) vs 40,000 km interval — +3,346 km over. Surfaced by the odometer single-source sweep; hidden previously by a stale odometer reading.</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Change gearbox oil (GL-4 75W-90 ONLY — GL-5 destroys the synchros) before departure.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>OI-108</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ADV-015</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>314546</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>SSOT fact gate (OVERRUN) · R23 · Service Checklist</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Transfer case oil OVERDUE</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>43,346 km on the oil (changed Feb 2025 @ 271,200 km at rebuild) vs 40,000 km interval — +3,346 km over.</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Change transfer case oil before departure.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>OI-108</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ADV-016</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>314546</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>SSOT fact gate (OVERRUN) · R23 · Service Checklist</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Rear differential oil OVERDUE</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>41,523 km on the oil (changed Apr 2025 @ 273,023 km) vs 40,000 km interval — +1,523 km over. Front diff oil (changed Jan 2026 @ 293,949 km, 20,597 km) is within interval.</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Change rear diff oil (80W-90) before departure.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>OI-108</t>
+          <t>OI-122</t>
         </is>
       </c>
     </row>

--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -9253,7 +9253,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Invoice line 'Replace all gear oils' R3,780.00 excl covers gearbox, transfer case, front diff and rear diff (all four, owner 20 Oct 2026); the three rows below are its cost-0 children.</t>
+          <t>Invoice line 'Replace all gear oils' R3,780.00 excl covers gearbox, transfer case, front diff and rear diff (all four, owner 20 Oct 2026); the three rows below are its cost-0 children. Grade: GL-4 (owner, 20 Oct 2026).</t>
         </is>
       </c>
     </row>
@@ -9282,6 +9282,11 @@
           <t>PW Auto Centre</t>
         </is>
       </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Grade: GL-4 (owner, 20 Oct 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
@@ -9308,6 +9313,11 @@
           <t>PW Auto Centre</t>
         </is>
       </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Grade: the correct diff oil, GL-5 per R13 (owner, 20 Oct 2026: 'the correct oils went in').</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
@@ -9332,6 +9342,11 @@
       <c r="F325" s="1" t="inlineStr">
         <is>
           <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Grade: the correct diff oil, GL-5 per R13 (owner, 20 Oct 2026: 'the correct oils went in').</t>
         </is>
       </c>
     </row>

--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -9408,7 +9408,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Front bearings repacked; rear bearings new.</t>
+          <t>All four bearings new (owner, 25 Oct 2026) - corrects the 20 Oct entry, which recorded the front bearings as repacked. Bearing kits are listed only for the rear on this invoice. Repack every 40,000 km (owner, 25 Oct 2026). OI-63 closed.</t>
         </is>
       </c>
     </row>

--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -17,9 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;R&quot;#,##0_);[Red]\(&quot;R&quot;#,##0\)"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -629,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I339"/>
+  <dimension ref="A1:I340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.59765625" customWidth="1" min="1" max="1"/>
@@ -9761,6 +9762,37 @@
       <c r="F339" s="1" t="inlineStr">
         <is>
           <t>4X4 Megaworld</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B340" s="27" t="n">
+        <v>315115</v>
+      </c>
+      <c r="C340" s="1" t="inlineStr">
+        <is>
+          <t>Dyno test + turbo nuts (oil sweat)</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="n">
+        <v>690</v>
+      </c>
+      <c r="F340" s="1" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Steve's Auto Clinic (SAC), 26 Oct 2026, R690 for the visit (owner). Dyno: 122.69kw @ 3407 rpm; 374.55Nm @ 2073 rpm (run T002 - current); run T001 120.32kw @ 3356 rpm; 376.08Nm @ 2114 rpm. First dyno after the Jun 2026 pump rebuild and injector recon. Turbo oil sweat at the large pipe (ADV-017) attended: new nuts fitted at the sweating joint - which joint not recorded (owner, 26 Oct 2026). OI-122 closed. Odometer from the owner.</t>
         </is>
       </c>
     </row>
@@ -10229,12 +10261,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Have a diesel/turbo workshop inspect: identify the pipe and where the oil comes from (turbo seal, oil feed or drain, or a pipe joint). Check the boost-pipe clamps (ADV-010) at the same visit.</t>
+          <t>Have a diesel/turbo workshop inspect: identify the pipe and where the oil comes from (turbo seal, oil feed or drain, or a pipe joint). Check the boost-pipe clamps (ADV-010) at the same visit. DONE 26 Oct 2026 @ 315,115 km: attended at Steve's Auto Clinic, new nuts fitted at the sweating joint (owner). OI-122 closed.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">

--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -17,10 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;R&quot;#,##0_);[Red]\(&quot;R&quot;#,##0\)"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -9774,7 +9773,7 @@
       </c>
       <c r="C340" s="1" t="inlineStr">
         <is>
-          <t>Dyno test + turbo nuts (oil sweat)</t>
+          <t>Dyno run + secure turbo flange bolts</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9792,7 +9791,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Steve's Auto Clinic (SAC), 26 Oct 2026, R690 for the visit (owner). Dyno: 122.69kw @ 3407 rpm; 374.55Nm @ 2073 rpm (run T002 - current); run T001 120.32kw @ 3356 rpm; 376.08Nm @ 2114 rpm. First dyno after the Jun 2026 pump rebuild and injector recon. Turbo oil sweat at the large pipe (ADV-017) attended: new nuts fitted at the sweating joint - which joint not recorded (owner, 26 Oct 2026). OI-122 closed. Odometer from the owner.</t>
+          <t>Steve's Auto Clinic CT CC tax invoice 123000, 26 Oct 2026, mileage 315115 (E1): one line 'Dynorun - secure turbo flange bolts', R600.00 excl + R90.00 VAT = R690.00. Dyno: 122.69kw @ 3407 rpm; 374.55Nm @ 2073 rpm (run T002 - current); run T001 120.32kw @ 3356 rpm; 376.08Nm @ 2114 rpm. First dyno after the Jun 2026 pump rebuild and injector recon. Turbo oil sweat at the large pipe (ADV-017): the turbo flange bolts were secured (invoice); the owner reports new nuts. OI-122 closed. Labour guarantee 6 months or 20,000 km (invoice terms).</t>
         </is>
       </c>
     </row>
@@ -10261,7 +10260,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Have a diesel/turbo workshop inspect: identify the pipe and where the oil comes from (turbo seal, oil feed or drain, or a pipe joint). Check the boost-pipe clamps (ADV-010) at the same visit. DONE 26 Oct 2026 @ 315,115 km: attended at Steve's Auto Clinic, new nuts fitted at the sweating joint (owner). OI-122 closed.</t>
+          <t>Have a diesel/turbo workshop inspect: identify the pipe and where the oil comes from (turbo seal, oil feed or drain, or a pipe joint). Check the boost-pipe clamps (ADV-010) at the same visit. DONE 26 Oct 2026 @ 315,115 km: turbo flange bolts secured at Steve's Auto Clinic (invoice 123000; owner reports new nuts). OI-122 closed.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
